--- a/reports/avuong_kttv/templates/A_VUONG_BM_BC_SO_LIEU_HANG_NGAY.xlsx
+++ b/reports/avuong_kttv/templates/A_VUONG_BM_BC_SO_LIEU_HANG_NGAY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Power Automate\Thuy_van_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{448BFC5C-8A15-4351-8E02-E60C427C12D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D8F0549-0C94-4336-8555-7D9541235E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,10 +150,10 @@
     </r>
   </si>
   <si>
-    <t>22/10/2026</t>
+    <t>24/10/2026</t>
   </si>
   <si>
-    <t>23/10/2026</t>
+    <t>25/10/2026</t>
   </si>
 </sst>
 </file>
@@ -927,13 +927,13 @@
         <v>8</v>
       </c>
       <c r="D6" s="9">
-        <v>354.95</v>
+        <v>354.26</v>
       </c>
       <c r="E6" s="12">
-        <v>15.96</v>
+        <v>28.33</v>
       </c>
       <c r="F6" s="11">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="G6" s="11">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>9</v>
       </c>
       <c r="D7" s="9">
-        <v>354.97</v>
+        <v>354.24</v>
       </c>
       <c r="E7" s="12">
-        <v>31.91</v>
+        <v>18.89</v>
       </c>
       <c r="F7" s="11">
-        <v>0</v>
+        <v>50.8</v>
       </c>
       <c r="G7" s="11">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>10</v>
       </c>
       <c r="D8" s="9">
-        <v>354.99</v>
+        <v>354.25</v>
       </c>
       <c r="E8" s="12">
-        <v>31.91</v>
+        <v>15.96</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
@@ -981,7 +981,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="9">
-        <v>355</v>
+        <v>354.26</v>
       </c>
       <c r="E9" s="12">
         <v>15.96</v>
@@ -999,10 +999,10 @@
         <v>12</v>
       </c>
       <c r="D10" s="9">
-        <v>355.01</v>
+        <v>354.28</v>
       </c>
       <c r="E10" s="12">
-        <v>17.53</v>
+        <v>31.91</v>
       </c>
       <c r="F10" s="11">
         <v>0</v>
@@ -1017,10 +1017,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="9">
-        <v>355.02</v>
+        <v>354.3</v>
       </c>
       <c r="E11" s="12">
-        <v>17.53</v>
+        <v>31.91</v>
       </c>
       <c r="F11" s="11">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>14</v>
       </c>
       <c r="D12" s="9">
-        <v>355.05</v>
+        <v>354.32</v>
       </c>
       <c r="E12" s="12">
-        <v>52.6</v>
+        <v>31.91</v>
       </c>
       <c r="F12" s="11">
         <v>0</v>
@@ -1053,13 +1053,13 @@
         <v>15</v>
       </c>
       <c r="D13" s="9">
-        <v>355.06</v>
+        <v>354.29</v>
       </c>
       <c r="E13" s="12">
-        <v>42.73</v>
+        <v>15.63</v>
       </c>
       <c r="F13" s="11">
-        <v>25.2</v>
+        <v>63.5</v>
       </c>
       <c r="G13" s="11">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>16</v>
       </c>
       <c r="D14" s="9">
-        <v>355.03</v>
+        <v>354.26</v>
       </c>
       <c r="E14" s="12">
-        <v>22.8</v>
+        <v>29.5</v>
       </c>
       <c r="F14" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G14" s="11">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>17</v>
       </c>
       <c r="D15" s="9">
-        <v>355</v>
+        <v>354.23</v>
       </c>
       <c r="E15" s="12">
-        <v>22.8</v>
+        <v>29.5</v>
       </c>
       <c r="F15" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G15" s="11">
         <v>0</v>
@@ -1107,13 +1107,13 @@
         <v>18</v>
       </c>
       <c r="D16" s="9">
-        <v>354.98</v>
+        <v>354.2</v>
       </c>
       <c r="E16" s="12">
-        <v>43.49</v>
+        <v>29.5</v>
       </c>
       <c r="F16" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G16" s="11">
         <v>0</v>
@@ -1125,13 +1125,13 @@
         <v>19</v>
       </c>
       <c r="D17" s="9">
-        <v>354.96</v>
+        <v>354.18</v>
       </c>
       <c r="E17" s="12">
-        <v>43.49</v>
+        <v>45.46</v>
       </c>
       <c r="F17" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G17" s="11">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>20</v>
       </c>
       <c r="D18" s="9">
-        <v>354.94</v>
+        <v>354.17</v>
       </c>
       <c r="E18" s="12">
-        <v>43.49</v>
+        <v>61.41</v>
       </c>
       <c r="F18" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G18" s="11">
         <v>0</v>
@@ -1161,13 +1161,13 @@
         <v>21</v>
       </c>
       <c r="D19" s="9">
-        <v>354.92</v>
+        <v>354.16</v>
       </c>
       <c r="E19" s="12">
-        <v>43.49</v>
+        <v>61.41</v>
       </c>
       <c r="F19" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G19" s="11">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>22</v>
       </c>
       <c r="D20" s="9">
-        <v>354.9</v>
+        <v>354.15</v>
       </c>
       <c r="E20" s="12">
-        <v>43.49</v>
+        <v>61.41</v>
       </c>
       <c r="F20" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G20" s="11">
         <v>0</v>
@@ -1197,13 +1197,13 @@
         <v>23</v>
       </c>
       <c r="D21" s="9">
-        <v>354.88</v>
+        <v>354.13</v>
       </c>
       <c r="E21" s="12">
-        <v>43.49</v>
+        <v>45.46</v>
       </c>
       <c r="F21" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G21" s="11">
         <v>0</v>
@@ -1215,13 +1215,13 @@
         <v>24</v>
       </c>
       <c r="D22" s="9">
-        <v>354.87</v>
+        <v>354.11</v>
       </c>
       <c r="E22" s="12">
-        <v>59.44</v>
+        <v>45.46</v>
       </c>
       <c r="F22" s="11">
-        <v>75.400000000000006</v>
+        <v>77.37</v>
       </c>
       <c r="G22" s="11">
         <v>0</v>
@@ -1235,13 +1235,13 @@
         <v>1</v>
       </c>
       <c r="D23" s="9">
-        <v>354.85</v>
+        <v>354.08</v>
       </c>
       <c r="E23" s="12">
-        <v>43.49</v>
+        <v>27.23</v>
       </c>
       <c r="F23" s="11">
-        <v>75.400000000000006</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="G23" s="11">
         <v>0</v>
@@ -1253,13 +1253,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="9">
-        <v>354.82</v>
+        <v>354.05</v>
       </c>
       <c r="E24" s="12">
-        <v>27.53</v>
+        <v>27.03</v>
       </c>
       <c r="F24" s="11">
-        <v>75.400000000000006</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G24" s="11">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="9">
-        <v>354.79</v>
+        <v>354.02</v>
       </c>
       <c r="E25" s="12">
-        <v>27.53</v>
+        <v>27.03</v>
       </c>
       <c r="F25" s="11">
-        <v>75.400000000000006</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G25" s="11">
         <v>0</v>
@@ -1289,13 +1289,13 @@
         <v>4</v>
       </c>
       <c r="D26" s="9">
-        <v>354.76</v>
+        <v>353.99</v>
       </c>
       <c r="E26" s="12">
-        <v>27.53</v>
+        <v>27.03</v>
       </c>
       <c r="F26" s="11">
-        <v>75.400000000000006</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G26" s="11">
         <v>0</v>
@@ -1307,13 +1307,13 @@
         <v>5</v>
       </c>
       <c r="D27" s="9">
-        <v>354.74</v>
+        <v>353.95</v>
       </c>
       <c r="E27" s="12">
-        <v>43.49</v>
+        <v>11.08</v>
       </c>
       <c r="F27" s="11">
-        <v>75.400000000000006</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G27" s="11">
         <v>0</v>
@@ -1325,13 +1325,13 @@
         <v>6</v>
       </c>
       <c r="D28" s="9">
-        <v>354.72</v>
+        <v>353.93</v>
       </c>
       <c r="E28" s="12">
-        <v>43.49</v>
+        <v>23.89</v>
       </c>
       <c r="F28" s="11">
-        <v>75.400000000000006</v>
+        <v>55.8</v>
       </c>
       <c r="G28" s="11">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>7</v>
       </c>
       <c r="D29" s="9">
-        <v>354.7</v>
+        <v>353.94</v>
       </c>
       <c r="E29" s="12">
-        <v>43.49</v>
+        <v>15.96</v>
       </c>
       <c r="F29" s="11">
-        <v>75.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="G29" s="11">
         <v>0</v>
@@ -8232,16 +8232,32 @@
       </c>
     </row>
     <row r="492" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B492" s="24"/>
-      <c r="C492" s="25"/>
-      <c r="D492" s="25"/>
-      <c r="E492" s="25"/>
+      <c r="B492" s="24">
+        <v>46318</v>
+      </c>
+      <c r="C492" s="25">
+        <v>29.838333333333299</v>
+      </c>
+      <c r="D492" s="25">
+        <v>57.095833333333402</v>
+      </c>
+      <c r="E492" s="25">
+        <v>0</v>
+      </c>
     </row>
     <row r="493" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B493" s="24"/>
-      <c r="C493" s="25"/>
-      <c r="D493" s="25"/>
-      <c r="E493" s="25"/>
+      <c r="B493" s="24">
+        <v>46319</v>
+      </c>
+      <c r="C493" s="25">
+        <v>31.6191666666667</v>
+      </c>
+      <c r="D493" s="25">
+        <v>54.888750000000002</v>
+      </c>
+      <c r="E493" s="25">
+        <v>0</v>
+      </c>
     </row>
     <row r="494" spans="2:5" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B494" s="24"/>
@@ -19381,7 +19397,7 @@
       </c>
       <c r="F1" s="13">
         <f>WEEKDAY(C6, 1)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -19400,11 +19416,11 @@
     <row r="3" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <f>ROUND((C6-B1)/7,0)+1</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="42" t="str">
         <f>_xlfn.CONCAT("Số liệu thủy văn tuần thứ ", A3, " năm ", A2)</f>
-        <v>Số liệu thủy văn tuần thứ 94 năm 2025</v>
+        <v>Số liệu thủy văn tuần thứ 95 năm 2025</v>
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
@@ -19442,19 +19458,19 @@
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="str">
         <f>CHOOSE(WEEKDAY(C6,2),"Thứ hai","Thứ ba","Thứ tư","Thứ năm ", "Thứ sáu", "Thứ bảy", "Chủ nhật")</f>
-        <v>Thứ sáu</v>
+        <v>Chủ nhật</v>
       </c>
       <c r="C6" s="19">
         <f t="shared" ref="C6:C10" si="0">C7-1</f>
-        <v>46311</v>
+        <v>46313</v>
       </c>
       <c r="D6" s="11">
         <f>VLOOKUP($C6, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>45.224166666666697</v>
+        <v>38.222083333333401</v>
       </c>
       <c r="E6" s="11">
         <f>VLOOKUP($C6, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>15.9716666666667</v>
+        <v>15.625</v>
       </c>
       <c r="F6" s="11">
         <f>VLOOKUP($C6, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19465,19 +19481,19 @@
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="str">
         <f t="shared" ref="B7:B12" si="1">CHOOSE(WEEKDAY(C7,2),"Thứ hai","Thứ ba","Thứ tư","Thứ năm ", "Thứ sáu", "Thứ bảy", "Chủ nhật")</f>
-        <v>Thứ bảy</v>
+        <v>Thứ hai</v>
       </c>
       <c r="C7" s="19">
         <f t="shared" si="0"/>
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="D7" s="11">
         <f>VLOOKUP($C7, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>42.897083333333299</v>
+        <v>44.499166666666703</v>
       </c>
       <c r="E7" s="11">
         <f>VLOOKUP($C7, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>16.304166666666699</v>
+        <v>36.462499999999999</v>
       </c>
       <c r="F7" s="11">
         <f>VLOOKUP($C7, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19488,19 +19504,19 @@
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>Chủ nhật</v>
+        <v>Thứ ba</v>
       </c>
       <c r="C8" s="19">
         <f t="shared" si="0"/>
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="D8" s="11">
         <f>VLOOKUP($C8, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>38.222083333333401</v>
+        <v>42.141249999999999</v>
       </c>
       <c r="E8" s="11">
         <f>VLOOKUP($C8, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>15.625</v>
+        <v>50.908333333333303</v>
       </c>
       <c r="F8" s="11">
         <f>VLOOKUP($C8, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19511,19 +19527,19 @@
     <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ hai</v>
+        <v>Thứ tư</v>
       </c>
       <c r="C9" s="19">
         <f t="shared" si="0"/>
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D9" s="11">
         <f>VLOOKUP($C9, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>44.499166666666703</v>
+        <v>39.835833333333298</v>
       </c>
       <c r="E9" s="11">
         <f>VLOOKUP($C9, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>36.462499999999999</v>
+        <v>50.4</v>
       </c>
       <c r="F9" s="11">
         <f>VLOOKUP($C9, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19534,19 +19550,19 @@
     <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ ba</v>
+        <v xml:space="preserve">Thứ năm </v>
       </c>
       <c r="C10" s="19">
         <f t="shared" si="0"/>
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="D10" s="11">
         <f>VLOOKUP($C10, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>42.141249999999999</v>
+        <v>35.360833333333296</v>
       </c>
       <c r="E10" s="11">
         <f>VLOOKUP($C10, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>50.908333333333303</v>
+        <v>51.316666666666698</v>
       </c>
       <c r="F10" s="11">
         <f>VLOOKUP($C10, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19557,19 +19573,19 @@
     <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>Thứ tư</v>
+        <v>Thứ sáu</v>
       </c>
       <c r="C11" s="19">
         <f>C12-1</f>
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="D11" s="11">
         <f>VLOOKUP($C11, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>39.835833333333298</v>
+        <v>29.838333333333299</v>
       </c>
       <c r="E11" s="11">
         <f>VLOOKUP($C11, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>50.4</v>
+        <v>57.095833333333402</v>
       </c>
       <c r="F11" s="11">
         <f>VLOOKUP($C11, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19580,18 +19596,18 @@
     <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">Thứ năm </v>
+        <v>Thứ bảy</v>
       </c>
       <c r="C12" s="19">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="D12" s="11">
         <f>VLOOKUP($C12, SolieuQtbngay!$B$6:$E$1980, 2,TRUE)</f>
-        <v>35.360833333333296</v>
+        <v>31.6191666666667</v>
       </c>
       <c r="E12" s="11">
         <f>VLOOKUP($C12, SolieuQtbngay!$B$6:$E$1980, 3)</f>
-        <v>51.316666666666698</v>
+        <v>54.888750000000002</v>
       </c>
       <c r="F12" s="11">
         <f>VLOOKUP($C12, SolieuQtbngay!$B$6:$E$1980, 4)</f>
@@ -19604,18 +19620,18 @@
         <f>_xlfn.CONCAT("Đặc trưng
 Tuần ", A3)</f>
         <v>Đặc trưng
-Tuần 94</v>
+Tuần 95</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="16">
         <f>MAX(D6:D12)</f>
-        <v>45.224166666666697</v>
+        <v>44.499166666666703</v>
       </c>
       <c r="E13" s="16">
         <f t="shared" ref="E13:F13" si="2">MAX(E6:E12)</f>
-        <v>51.316666666666698</v>
+        <v>57.095833333333402</v>
       </c>
       <c r="F13" s="16">
         <f t="shared" si="2"/>
@@ -19629,11 +19645,11 @@
       </c>
       <c r="D14" s="16">
         <f>AVERAGE(D6:D12)</f>
-        <v>41.168630952380958</v>
+        <v>37.359523809523814</v>
       </c>
       <c r="E14" s="16">
         <f t="shared" ref="E14:F14" si="3">AVERAGE(E6:E12)</f>
-        <v>33.855476190476203</v>
+        <v>45.242440476190488</v>
       </c>
       <c r="F14" s="16">
         <f t="shared" si="3"/>
@@ -19647,7 +19663,7 @@
       </c>
       <c r="D15" s="16">
         <f>MIN(D6:D12)</f>
-        <v>35.360833333333296</v>
+        <v>29.838333333333299</v>
       </c>
       <c r="E15" s="16">
         <f t="shared" ref="E15:F15" si="4">MIN(E6:E12)</f>
